--- a/result/morris/morris_first_inf_ONLY_Signed_N512_seed42.xlsx
+++ b/result/morris/morris_first_inf_ONLY_Signed_N512_seed42.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,65 +453,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.98079427083332</v>
+        <v>-20.52935112847224</v>
       </c>
       <c r="C2" t="n">
-        <v>33.17415364583334</v>
+        <v>26.02913411458334</v>
       </c>
       <c r="D2" t="n">
-        <v>24.63932340191696</v>
+        <v>29.34356674221971</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-25.25412326388886</v>
+        <v>20.54313151041664</v>
       </c>
       <c r="C3" t="n">
-        <v>27.33919270833331</v>
+        <v>23.26969401041664</v>
       </c>
       <c r="D3" t="n">
-        <v>30.04399363594528</v>
+        <v>24.99802674486972</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.45079210069444</v>
+        <v>11.89322916666666</v>
       </c>
       <c r="C4" t="n">
-        <v>23.19981553819444</v>
+        <v>19.95952690972222</v>
       </c>
       <c r="D4" t="n">
-        <v>25.57815002833878</v>
+        <v>29.91952201420751</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.42865668402778</v>
+        <v>9.630859375</v>
       </c>
       <c r="C5" t="n">
-        <v>23.05799696180556</v>
+        <v>19.72992621527778</v>
       </c>
       <c r="D5" t="n">
-        <v>29.74653104869758</v>
+        <v>27.11721605931486</v>
       </c>
     </row>
     <row r="6">
@@ -521,125 +521,141 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.9152018229166663</v>
+        <v>-2.534884982638891</v>
       </c>
       <c r="C6" t="n">
-        <v>7.971299913194444</v>
+        <v>11.20502387152779</v>
       </c>
       <c r="D6" t="n">
-        <v>19.04906233792022</v>
+        <v>20.29273804546424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.068467881944446</v>
+        <v>5.927571614583335</v>
       </c>
       <c r="C7" t="n">
-        <v>4.189670138888892</v>
+        <v>10.66292317708334</v>
       </c>
       <c r="D7" t="n">
-        <v>10.07779988774341</v>
+        <v>17.20980025032305</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dispersal__wind_min</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.172471788194444</v>
+        <v>-1.008409288194444</v>
       </c>
       <c r="C8" t="n">
-        <v>3.155761718750002</v>
+        <v>7.583279079861116</v>
       </c>
       <c r="D8" t="n">
-        <v>8.923342583222603</v>
+        <v>24.92683587697676</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>dispersal__wind_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.697916666666676</v>
+        <v>-1.360460069444443</v>
       </c>
       <c r="C9" t="n">
-        <v>2.927951388888901</v>
+        <v>6.646050347222227</v>
       </c>
       <c r="D9" t="n">
-        <v>2.762853471533184</v>
+        <v>15.98706433494498</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.082411024305556</v>
+        <v>-1.631510416666667</v>
       </c>
       <c r="C10" t="n">
-        <v>2.90185546875</v>
+        <v>4.069878472222223</v>
       </c>
       <c r="D10" t="n">
-        <v>11.99105037626731</v>
+        <v>16.4976848797761</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.061469184027778</v>
+        <v>1.416015625</v>
       </c>
       <c r="C11" t="n">
-        <v>2.376790364583333</v>
+        <v>3.588107638888893</v>
       </c>
       <c r="D11" t="n">
-        <v>8.23535994620552</v>
+        <v>17.34992623916606</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>incubation__spl_end</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6626519097222223</v>
+        <v>2.799804687500007</v>
       </c>
       <c r="C12" t="n">
-        <v>1.929144965277778</v>
+        <v>2.799804687500007</v>
       </c>
       <c r="D12" t="n">
-        <v>10.29433174545355</v>
+        <v>0.389850747806994</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6105685763888887</v>
+        <v>1.764702690972222</v>
       </c>
       <c r="C13" t="n">
-        <v>1.590603298611111</v>
+        <v>2.33447265625</v>
       </c>
       <c r="D13" t="n">
-        <v>4.782768010883643</v>
+        <v>10.40732744784452</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sporulation__MP_min</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.8862304687499998</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.590983072916667</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.367272645484587</v>
       </c>
     </row>
   </sheetData>
